--- a/Deliverables/sprint-01/planning-documents.xlsx
+++ b/Deliverables/sprint-01/planning-documents.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="182">
   <si>
     <t>Project Name</t>
   </si>
@@ -447,10 +447,10 @@
     <t>Project Mission</t>
   </si>
   <si>
-    <t>The reason of existence of the envisioned product (beyond this project).</t>
-  </si>
-  <si>
-    <t>The mission of this particular project (in the context of the product vision).</t>
+    <t>LLMs are a fantastic tool to interview research subjects at scale, which previously had to be done by human researchers. This method generates unstructured interview dialogues which must then be processed and analysed manually. The goal of this project is to use LLMs to also automate the analysis part, enabling policy researchers to feed their interview corpus to our tool and obtain not only the thematic analysis, but also relevant insights derived from the demographic data of the respondents. This way, we seek to bridge the gap between quantitative and qualitative policy research.</t>
+  </si>
+  <si>
+    <t>To engineer a secure, open-source tool that ingests thousands of subject interviews about a policy topic and produces an accurate thematic analysis breakdown. The core is a multi-stage LLM pipeline that extracts quotes, codes them into themes, clusters and ranks those themes, and cross-references them against respondent demographic dimensions. Results are surfaced through a lightweight frontend and exportable in structured formats. We also provide direct reference back to the corpus, so researchers can see which interviews most strongly manifest a particular theme or demographic combination. We build on QuaLLM by incorporating this demographic layer, inferring how discovered themes distribute across the profile of research subjects, and surfacing patterns that a purely manual process would likely miss.</t>
   </si>
   <si>
     <t>Term</t>
@@ -459,6 +459,30 @@
     <t>Definition</t>
   </si>
   <si>
+    <t>Corpus / Dataset</t>
+  </si>
+  <si>
+    <t>The 1,058 LLM-led interviews on the economic impact of AI provided by the Industry Partner. Format: JSON</t>
+  </si>
+  <si>
+    <t>Demographic Data</t>
+  </si>
+  <si>
+    <t>Categorical variables describing each subject in the Corpus; has been partially sanitized by Industry partner, but must be handled with care. Absolutely should not be downloaded or uploaded to third parties. Format: CSV</t>
+  </si>
+  <si>
+    <t>Thematic Analysis</t>
+  </si>
+  <si>
+    <t>The qualitative method of identifying and analyzing patterns of meaning (themes) in a dataset. These themes should be followed by a short description and some quantitative measures of prevalence in the dataset.</t>
+  </si>
+  <si>
+    <t>QuaLLM</t>
+  </si>
+  <si>
+    <t>The specific LLM-based framework serving as the baseline architecture for our project. Suggested by Dr. Kaiser, can be seen on Rao et al.</t>
+  </si>
+  <si>
     <t>Sprint #</t>
   </si>
   <si>
@@ -466,6 +490,9 @@
   </si>
   <si>
     <t>Meeting with industry partner, designing the logo, setting up the project</t>
+  </si>
+  <si>
+    <t>Ingesting the interview dataset provided by the industry partner, working on the Architecture Description document, and delivering a first prototype that successfully passes text through a basic LLM endpoint.</t>
   </si>
   <si>
     <t>Story Points Realized</t>
@@ -1507,25 +1534,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="48" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B1" s="78" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2">
@@ -1539,7 +1566,7 @@
     </row>
     <row r="3">
       <c r="A3" s="55" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -1559,7 +1586,7 @@
     </row>
     <row r="5">
       <c r="A5" s="58" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -1585,7 +1612,7 @@
     </row>
     <row r="7">
       <c r="A7" s="61" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B7" s="79"/>
       <c r="C7" s="63"/>
@@ -1600,11 +1627,11 @@
       <c r="C8" s="54"/>
       <c r="D8" s="54"/>
       <c r="E8" s="64" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F8" s="54"/>
       <c r="G8" s="64" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
@@ -1706,7 +1733,7 @@
     </row>
     <row r="14">
       <c r="A14" s="69" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B14" s="70"/>
       <c r="C14" s="71"/>
@@ -1890,7 +1917,7 @@
       <c r="A33" s="65"/>
       <c r="B33" s="36"/>
       <c r="C33" s="77" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D33" s="60"/>
       <c r="E33" s="36"/>
@@ -1930,13 +1957,13 @@
         <v>64</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C1" s="49" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
@@ -2074,10 +2101,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2">
@@ -2184,16 +2211,16 @@
         <v>64</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>71</v>
@@ -2381,7 +2408,7 @@
         <v>First Name</v>
       </c>
       <c r="C1" s="84" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D1" s="85"/>
       <c r="E1" s="86"/>
@@ -2474,7 +2501,7 @@
         <v>0.0</v>
       </c>
       <c r="F6" s="103" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G6" s="94"/>
       <c r="H6" s="94"/>
@@ -2494,7 +2521,7 @@
         <v>1.0</v>
       </c>
       <c r="F7" s="103" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="G7" s="97"/>
       <c r="H7" s="97"/>
@@ -2514,7 +2541,7 @@
         <v>2.0</v>
       </c>
       <c r="F8" s="103" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G8" s="94"/>
       <c r="H8" s="94"/>
@@ -2534,7 +2561,7 @@
         <v>3.0</v>
       </c>
       <c r="F9" s="103" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G9" s="97"/>
       <c r="H9" s="97"/>
@@ -2554,7 +2581,7 @@
         <v>5.0</v>
       </c>
       <c r="F10" s="103" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G10" s="94"/>
       <c r="H10" s="94"/>
@@ -2568,7 +2595,7 @@
         <v>8.0</v>
       </c>
       <c r="F11" s="103" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G11" s="97"/>
       <c r="H11" s="97"/>
@@ -2582,7 +2609,7 @@
         <v>13.0</v>
       </c>
       <c r="F12" s="103" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G12" s="94"/>
       <c r="H12" s="94"/>
@@ -2599,7 +2626,7 @@
     </row>
     <row r="14">
       <c r="A14" s="104" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B14" s="105"/>
       <c r="C14" s="105"/>
@@ -2621,7 +2648,7 @@
     </row>
     <row r="16">
       <c r="A16" s="107" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B16" s="108"/>
       <c r="C16" s="108"/>
@@ -2633,7 +2660,7 @@
     </row>
     <row r="17">
       <c r="A17" s="109" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B17" s="106"/>
       <c r="C17" s="106"/>
@@ -2645,7 +2672,7 @@
     </row>
     <row r="18">
       <c r="A18" s="107" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B18" s="108"/>
       <c r="C18" s="108"/>
@@ -3751,20 +3778,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="A2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3"/>
@@ -3847,10 +3890,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="44" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2">
@@ -3858,7 +3901,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -3866,7 +3909,9 @@
         <f t="shared" ref="A3:A16" si="1">A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="45">
@@ -3995,17 +4040,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="44" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="45">
         <v>1.0</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="45">
@@ -4111,7 +4158,7 @@
     <row r="18">
       <c r="A18" s="45"/>
       <c r="B18" s="47" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19">
@@ -4144,25 +4191,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="48" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2">
@@ -4176,7 +4223,7 @@
     </row>
     <row r="3">
       <c r="A3" s="55" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="57"/>
@@ -4196,7 +4243,7 @@
     </row>
     <row r="5">
       <c r="A5" s="58" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B5" s="59"/>
       <c r="C5" s="36"/>
@@ -4222,7 +4269,7 @@
     </row>
     <row r="7">
       <c r="A7" s="61" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B7" s="62"/>
       <c r="C7" s="63"/>
@@ -4237,11 +4284,11 @@
       <c r="C8" s="54"/>
       <c r="D8" s="54"/>
       <c r="E8" s="64" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F8" s="54"/>
       <c r="G8" s="64" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
@@ -4343,7 +4390,7 @@
     </row>
     <row r="14">
       <c r="A14" s="69" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B14" s="70"/>
       <c r="C14" s="71"/>
@@ -4536,7 +4583,7 @@
       <c r="A33" s="65"/>
       <c r="B33" s="74"/>
       <c r="C33" s="77" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D33" s="60"/>
       <c r="E33" s="36"/>
